--- a/data/trans_dic/LAWTONB_2R3-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/LAWTONB_2R3-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia moderada o superior</t>
+          <t>Población con dependencia moderada o superior (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,89; 17,42</t>
+          <t>10,79; 17,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,3; 27,94</t>
+          <t>19,22; 28,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,35; 24,72</t>
+          <t>16,13; 24,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22,63; 31,55</t>
+          <t>22,94; 31,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,55; 22,66</t>
+          <t>16,36; 23,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,58; 32,08</t>
+          <t>24,62; 32,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,26; 31,77</t>
+          <t>23,58; 32,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>35,19; 41,47</t>
+          <t>35,42; 41,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,04; 19,97</t>
+          <t>15,26; 20,01</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23,42; 29,2</t>
+          <t>23,49; 29,18</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21,4; 27,64</t>
+          <t>21,6; 27,59</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>31,53; 36,62</t>
+          <t>31,96; 37,26</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,95; 19,61</t>
+          <t>5,81; 19,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,52; 22,14</t>
+          <t>8,5; 23,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,09; 11,03</t>
+          <t>4,29; 11,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,81; 13,45</t>
+          <t>7,42; 13,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,28; 23,02</t>
+          <t>5,52; 24,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,1; 20,37</t>
+          <t>5,0; 19,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,28; 21,47</t>
+          <t>9,81; 21,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,38; 14,76</t>
+          <t>2,73; 14,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,96; 18,21</t>
+          <t>6,82; 18,13</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,03; 19,4</t>
+          <t>9,08; 18,85</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,23; 15,15</t>
+          <t>8,04; 14,97</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,52; 12,81</t>
+          <t>3,66; 12,75</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,33</t>
+          <t>0,0; 21,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,7</t>
+          <t>0,0; 26,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,23; 23,0</t>
+          <t>3,42; 23,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,84; 11,65</t>
+          <t>2,65; 11,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,25; 31,16</t>
+          <t>3,25; 29,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,42; 37,39</t>
+          <t>4,51; 38,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,71</t>
+          <t>3,05; 28,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,4; 15,44</t>
+          <t>5,44; 15,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,09; 18,8</t>
+          <t>2,9; 19,07</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,17; 23,52</t>
+          <t>4,23; 23,97</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,37; 19,83</t>
+          <t>3,98; 20,48</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,8; 11,32</t>
+          <t>4,88; 10,84</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,24; 15,93</t>
+          <t>10,21; 16,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,15; 24,86</t>
+          <t>17,41; 24,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,64; 17,98</t>
+          <t>12,41; 17,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,3; 19,11</t>
+          <t>14,16; 19,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,58; 21,8</t>
+          <t>15,61; 21,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,7; 29,11</t>
+          <t>22,91; 29,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,28; 27,24</t>
+          <t>20,4; 26,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,73; 29,17</t>
+          <t>12,23; 29,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,09; 18,44</t>
+          <t>13,97; 18,37</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21,09; 25,93</t>
+          <t>21,19; 26,33</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,65; 22,24</t>
+          <t>17,79; 22,36</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,07; 23,69</t>
+          <t>12,03; 23,59</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia moderada o superior</t>
+          <t>Población con dependencia moderada o superior (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>40654; 65027</t>
+          <t>40285; 64813</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>79973; 115769</t>
+          <t>79640; 117544</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>57872; 87501</t>
+          <t>57088; 85903</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>60148; 83882</t>
+          <t>60986; 84153</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>97259; 133209</t>
+          <t>96134; 136009</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>155970; 203536</t>
+          <t>156241; 203522</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>129018; 176246</t>
+          <t>130838; 177719</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>175216; 206459</t>
+          <t>176347; 205425</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>144551; 191939</t>
+          <t>146607; 192291</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>245648; 306305</t>
+          <t>246412; 306126</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>194456; 251132</t>
+          <t>196272; 250671</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>240818; 279640</t>
+          <t>244102; 284583</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5237; 17271</t>
+          <t>5121; 17337</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10113; 26278</t>
+          <t>10083; 27471</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7877; 21244</t>
+          <t>8261; 22440</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21300; 36670</t>
+          <t>20220; 36245</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3287; 14319</t>
+          <t>3434; 15484</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5065; 16921</t>
+          <t>4158; 16456</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17453; 40375</t>
+          <t>18446; 41303</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10800; 67021</t>
+          <t>12390; 67613</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10458; 27369</t>
+          <t>10248; 27253</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18211; 39142</t>
+          <t>18321; 38033</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31338; 57643</t>
+          <t>30608; 56975</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25570; 93106</t>
+          <t>26579; 92676</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 8377</t>
+          <t>0; 8867</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 6831</t>
+          <t>0; 7041</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>939; 9667</t>
+          <t>1438; 9687</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2931; 12023</t>
+          <t>2738; 11530</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>874; 8376</t>
+          <t>875; 7822</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>984; 8318</t>
+          <t>1004; 8465</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 9669</t>
+          <t>1027; 9516</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3854; 11013</t>
+          <t>3882; 11094</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2107; 12797</t>
+          <t>1973; 12981</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2035; 11483</t>
+          <t>2065; 11704</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3311; 15014</t>
+          <t>3014; 15502</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8378; 19755</t>
+          <t>8518; 18926</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>51447; 80020</t>
+          <t>51284; 80384</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>95990; 139114</t>
+          <t>97438; 137651</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>74377; 105813</t>
+          <t>73015; 105247</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>91783; 122619</t>
+          <t>90887; 122401</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>105422; 147546</t>
+          <t>105642; 146624</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>167923; 215387</t>
+          <t>169489; 217566</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>157480; 211538</t>
+          <t>158401; 209556</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>120009; 298489</t>
+          <t>125137; 297673</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>166149; 217492</t>
+          <t>164711; 216682</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>274041; 336974</t>
+          <t>275388; 342098</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>240870; 303571</t>
+          <t>242822; 305192</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>217623; 394503</t>
+          <t>200321; 392729</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/LAWTONB_2R3-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/LAWTONB_2R3-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,1%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,79; 17,37</t>
+          <t>10,97; 17,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,22; 28,36</t>
+          <t>19,07; 27,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,13; 24,27</t>
+          <t>16,09; 24,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22,94; 31,66</t>
+          <t>22,06; 30,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,36; 23,14</t>
+          <t>16,54; 23,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,62; 32,07</t>
+          <t>24,57; 31,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,58; 32,04</t>
+          <t>23,62; 31,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>35,42; 41,26</t>
+          <t>35,44; 41,69</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,26; 20,01</t>
+          <t>14,93; 19,89</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23,49; 29,18</t>
+          <t>23,38; 29,03</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21,6; 27,59</t>
+          <t>21,38; 27,38</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>31,96; 37,26</t>
+          <t>31,6; 36,72</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,81; 19,68</t>
+          <t>6,1; 19,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,5; 23,15</t>
+          <t>7,83; 22,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,29; 11,66</t>
+          <t>4,33; 11,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,42; 13,29</t>
+          <t>7,73; 13,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,52; 24,89</t>
+          <t>5,27; 23,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,0; 19,81</t>
+          <t>5,3; 21,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,81; 21,96</t>
+          <t>9,8; 21,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,73; 14,89</t>
+          <t>11,83; 17,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,82; 18,13</t>
+          <t>7,21; 18,02</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,08; 18,85</t>
+          <t>8,5; 19,26</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,04; 14,97</t>
+          <t>8,04; 15,0</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,66; 12,75</t>
+          <t>10,21; 14,36</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,53</t>
+          <t>0,0; 20,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,49</t>
+          <t>0,0; 24,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,42; 23,05</t>
+          <t>3,65; 24,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,65; 11,17</t>
+          <t>3,31; 11,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,25; 29,1</t>
+          <t>3,25; 29,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,51; 38,05</t>
+          <t>4,49; 36,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,05; 28,26</t>
+          <t>3,09; 30,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,44; 15,55</t>
+          <t>5,75; 15,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,9; 19,07</t>
+          <t>3,02; 19,04</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,23; 23,97</t>
+          <t>4,08; 23,28</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,98; 20,48</t>
+          <t>4,66; 20,89</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,88; 10,84</t>
+          <t>5,28; 11,83</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>22,92%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,21; 16,0</t>
+          <t>10,51; 16,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,41; 24,6</t>
+          <t>17,04; 24,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,41; 17,89</t>
+          <t>12,45; 17,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,16; 19,07</t>
+          <t>13,85; 18,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,61; 21,66</t>
+          <t>15,63; 21,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,91; 29,41</t>
+          <t>22,79; 29,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,4; 26,99</t>
+          <t>20,43; 27,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,23; 29,09</t>
+          <t>26,06; 30,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,97; 18,37</t>
+          <t>13,99; 18,29</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21,19; 26,33</t>
+          <t>20,87; 26,04</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,79; 22,36</t>
+          <t>17,72; 22,08</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,03; 23,59</t>
+          <t>21,41; 24,68</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>71199</t>
+          <t>74475</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>191111</t>
+          <t>205842</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>262310</t>
+          <t>280317</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>40285; 64813</t>
+          <t>40920; 66920</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>79640; 117544</t>
+          <t>79028; 114918</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>57088; 85903</t>
+          <t>56953; 85038</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>60986; 84153</t>
+          <t>63171; 86112</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>96134; 136009</t>
+          <t>97205; 136238</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>156241; 203522</t>
+          <t>155885; 201524</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>130838; 177719</t>
+          <t>131056; 176246</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>176347; 205425</t>
+          <t>189822; 223299</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>146607; 192291</t>
+          <t>143509; 191124</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>246412; 306126</t>
+          <t>245258; 304518</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>196272; 250671</t>
+          <t>194275; 248773</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>244102; 284583</t>
+          <t>259728; 301835</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28693</t>
+          <t>30899</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>34680</t>
+          <t>40099</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>63374</t>
+          <t>70998</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5121; 17337</t>
+          <t>5377; 17280</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10083; 27471</t>
+          <t>9290; 26235</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8261; 22440</t>
+          <t>8336; 22769</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20220; 36245</t>
+          <t>23440; 40891</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3434; 15484</t>
+          <t>3277; 14787</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4158; 16456</t>
+          <t>4405; 17536</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18446; 41303</t>
+          <t>18425; 40771</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12390; 67613</t>
+          <t>32627; 49274</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10248; 27253</t>
+          <t>10837; 27078</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18321; 38033</t>
+          <t>17150; 38852</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30608; 56975</t>
+          <t>30609; 57105</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26579; 92676</t>
+          <t>59117; 83139</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6162</t>
+          <t>7577</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6942</t>
+          <t>8078</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13104</t>
+          <t>15654</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 8867</t>
+          <t>0; 8413</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 7041</t>
+          <t>0; 6634</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1438; 9687</t>
+          <t>1534; 10289</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2738; 11530</t>
+          <t>3877; 13306</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>875; 7822</t>
+          <t>873; 7911</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1004; 8465</t>
+          <t>1000; 8145</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1027; 9516</t>
+          <t>1039; 10275</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3882; 11094</t>
+          <t>4766; 13039</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1973; 12981</t>
+          <t>2058; 12959</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2065; 11704</t>
+          <t>1993; 11367</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3014; 15502</t>
+          <t>3529; 15814</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8518; 18926</t>
+          <t>10567; 23649</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>106055</t>
+          <t>112951</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>232733</t>
+          <t>254018</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>338788</t>
+          <t>366969</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>51284; 80384</t>
+          <t>52804; 81300</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>97438; 137651</t>
+          <t>95353; 138893</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>73015; 105247</t>
+          <t>73284; 105186</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>90887; 122401</t>
+          <t>97878; 129684</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>105642; 146624</t>
+          <t>105823; 147711</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>169489; 217566</t>
+          <t>168604; 215774</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>158401; 209556</t>
+          <t>158675; 210016</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>125137; 297673</t>
+          <t>233002; 273041</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>164711; 216682</t>
+          <t>164992; 215710</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>275388; 342098</t>
+          <t>271187; 338358</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>242822; 305192</t>
+          <t>241938; 301381</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>200321; 392729</t>
+          <t>342669; 395085</t>
         </is>
       </c>
     </row>
